--- a/site/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,34 +605,320 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+          <t>h_01KYH5J2C920WJHY3GX2SPAXGF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH5J2C920WJHY3GX2SPAXGF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Access Policy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KYH5KGESHGBJAPEWDKSRJQZQ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH5KGESHGBJAPEWDKSRJQZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Attribute Policy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KYH5NRRXFA22FNPYXSPDNJ1T</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH5NRRXFA22FNPYXSPDNJ1T</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Required Applications</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KYH5SMPSCZE0R7XKEMWEKEJN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH5SMPSCZE0R7XKEMWEKEJN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Forbidden Applications</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KYH5W5Q36CQA05K8FKWMRBY9</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH5W5Q36CQA05K8FKWMRBY9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Group Policy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KYH5XTFKDWDJFVYF27QS7Y5D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH5XTFKDWDJFVYF27QS7Y5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Required Groups</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KTC1YYZB4SX49NJGZ8WWAPM3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KTC1YYZB4SX49NJGZ8WWAPM3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Forbidden Groups</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KTC1YYZBDABRKNE34MJ6PQ8J</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KTC1YYZBDABRKNE34MJ6PQ8J</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Directory Policy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KYH61D515Q1DKWGNG3BPEKG7</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH61D515Q1DKWGNG3BPEKG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Attribute Policy</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KYH651N3K30AKMN83K0XTFWJ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH651N3K30AKMN83K0XTFWJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ITSM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KYH68706XB3Y197VJAA8JS5S</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH68706XB3Y197VJAA8JS5S</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Application Configuration</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KYH69NE1Q8TJH5D4FQ8KDTWY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYH69NE1Q8TJH5D4FQ8KDTWY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Watchdog Insights</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ITSM Dashboard Created by Watchdog</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KYHCGS24V5S08C61BD11E98N</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-to-Entra-ID-Integration/#h_01KYHCGS24V5S08C61BD11E98N</t>
         </is>
       </c>
     </row>
